--- a/GWD Data/BW Casing Pipes.xlsx
+++ b/GWD Data/BW Casing Pipes.xlsx
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613B5C34-A2D6-4826-965C-59B59FDAB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5CB606-6F87-4E2B-8EAF-76A34B5CB9A6}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/BW Casing Pipes.xlsx
+++ b/GWD Data/BW Casing Pipes.xlsx
@@ -795,7 +795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD5CB606-6F87-4E2B-8EAF-76A34B5CB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{480E9E22-D6A2-4DE8-8242-D7EB3583B9A6}">
   <dimension ref="A1:F287"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
